--- a/data/trans_bre/P1802_2016_2023-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1802_2016_2023-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,06</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 12,14</t>
+          <t>-2,11; 11,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 16,05</t>
+          <t>3,37; 16,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 69,43</t>
+          <t>-9,01; 69,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 64,26</t>
+          <t>10,4; 68,03</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,95</t>
+          <t>-1,08; 8,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,82</t>
+          <t>2,08; 10,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 67,12</t>
+          <t>-5,89; 66,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 124,55</t>
+          <t>14,65; 120,54</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 7,12</t>
+          <t>-1,42; 6,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 10,42</t>
+          <t>-1,36; 10,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 125,78</t>
+          <t>-17,19; 134,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 56,42</t>
+          <t>-5,68; 51,52</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-31,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 9,62</t>
+          <t>-3,04; 9,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 1,03</t>
+          <t>-5,54; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 59,48</t>
+          <t>-13,82; 59,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 7,0</t>
+          <t>-29,83; 48,07</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-7,33</t>
+          <t>-6,21</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-56,72%</t>
+          <t>-52,84%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 6,77</t>
+          <t>-7,99; 6,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -3,2</t>
+          <t>-10,99; -2,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 45,73</t>
+          <t>-36,14; 44,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-72,64; -29,69</t>
+          <t>-71,62; -22,15</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 13,5</t>
+          <t>0,65; 13,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 8,31</t>
+          <t>-2,74; 8,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 119,09</t>
+          <t>2,45; 132,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 59,91</t>
+          <t>-13,84; 62,92</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,55%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,94</t>
+          <t>2,88; 10,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 7,08</t>
+          <t>1,8; 10,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,8; 117,05</t>
+          <t>22,69; 119,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 36,96</t>
+          <t>8,15; 62,28</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-23,8</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-76,94%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,13</t>
+          <t>1,76; 9,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 1,68</t>
+          <t>-1,08; 3,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 71,39</t>
+          <t>9,96; 72,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-90,49; 28,56</t>
+          <t>-14,95; 77,08</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-21,43%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,2</t>
+          <t>2,75; 6,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 2,08</t>
+          <t>1,89; 5,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,14; 46,19</t>
+          <t>17,93; 47,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 13,29</t>
+          <t>11,53; 37,62</t>
         </is>
       </c>
     </row>
